--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>Setting</t>
   </si>
@@ -554,7 +554,7 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="51.714285714285715" customWidth="1"/>
+    <col min="1" max="1" width="42.142857142857146" customWidth="1"/>
     <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -576,6 +576,9 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -587,6 +590,9 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
@@ -612,6 +618,9 @@
       <c r="A5" t="s">
         <v>19</v>
       </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -622,6 +631,9 @@
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>

--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -1,141 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="RunConfig" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Tags" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="TestConfigs" state="visible" r:id="rId6"/>
+    <sheet name="RunConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tags" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TestConfigs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>emulator</t>
-  </si>
-  <si>
-    <t>emulator or real_device - matches config/config.yaml</t>
-  </si>
-  <si>
-    <t>Suite</t>
-  </si>
-  <si>
-    <t>Enabled</t>
-  </si>
-  <si>
-    <t>Smoke</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>FilePath</t>
-  </si>
-  <si>
-    <t>smoke</t>
-  </si>
-  <si>
-    <t>regression</t>
-  </si>
-  <si>
-    <t>Date Added</t>
-  </si>
-  <si>
-    <t>tests/sale_order/test_create_sale_order.py</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>tests/sale_order/test_split_payment.py</t>
-  </si>
-  <si>
-    <t>tests/sale_return/test_sale_return.py</t>
-  </si>
-  <si>
-    <t>tests/sales_history/test_void_payment.py</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>tests/sales_history/test_edit_order.py</t>
-  </si>
-  <si>
-    <t>ConfigName</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>clock_in_pin</t>
-  </si>
-  <si>
-    <t>PIN used for Clock In on the emulator's Demo Admin account</t>
-  </si>
-  <si>
-    <t>discount_percent</t>
-  </si>
-  <si>
-    <t>Default Additional Discount percentage applied in sale order tests</t>
-  </si>
-  <si>
-    <t>tobacco_product_1_upc</t>
-  </si>
-  <si>
-    <t>First MSA/tobacco product UPC (triggers age verification)</t>
-  </si>
-  <si>
-    <t>tobacco_product_2_upc</t>
-  </si>
-  <si>
-    <t>Second MSA/tobacco product UPC (age verification must not reappear)</t>
-  </si>
-  <si>
-    <t>age_verification_dob</t>
-  </si>
-  <si>
-    <t>01/01/1990</t>
-  </si>
-  <si>
-    <t>DOB entered to pass age verification (MM/DD/YYYY)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -154,21 +45,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -493,240 +443,570 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col width="13.57142857142857" customWidth="1" min="1" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>emulator</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>emulator or real_device - matches config/config.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="42.142857142857146" customWidth="1"/>
-    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
+    <col width="42.14285714285715" customWidth="1" min="1" max="1"/>
+    <col width="13.57142857142857" customWidth="1" min="2" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FilePath</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_create_sale_order.py</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_split_payment.py</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tests/sale_return/test_sale_return.py</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tests/sales_history/test_void_payment.py</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tests/sales_history/test_edit_order.py</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_park_order.py</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_order_discounts.py</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_resume_parked_order.py</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_order_discount_edge_cases.py</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_cart_math_and_actions.py</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_cash_payment_edge_cases.py</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_age_verification_boundary.py</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tests/sale_return/test_partial_return.py</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tests/sale_order/test_cart_discarded_on_navigation.py</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tests/shift/test_lock_screen.py</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="21.142857142857142" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
-    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
+    <col width="21.14285714285714" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="42.14285714285715" customWidth="1" min="3" max="3"/>
+    <col width="13.57142857142857" customWidth="1" min="4" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ConfigName</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clock_in_pin</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1234</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PIN used for Clock In on the emulator's Demo Admin account</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>discount_percent</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Default Additional Discount percentage applied in sale order tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tobacco_product_1_upc</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>4210691878</v>
       </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>First MSA/tobacco product UPC (triggers age verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tobacco_product_2_upc</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2194227147</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Second MSA/tobacco product UPC (age verification must not reappear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>age_verification_dob</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01/01/1990</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DOB entered to pass age verification (MM/DD/YYYY)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>